--- a/outputs/evaluation/decision/v1/CF_M01/run_1/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_1/CF_M01_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3333</v>
+        <v>0.625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.7143</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8778</v>
+        <v>0.9237</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9302</v>
+        <v>0.9651</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3333</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>0.7143</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,34 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
         <v>6</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,28 +974,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8673</v>
+        <v>0.8138</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1009,137 +1009,392 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8603</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
+          <t>The only component that interacts directly with the presentation layer is the Api Gateway module. This is because the Api Gateway microservices design pattern is followed. This design pattern allows only one component to interact between users and the services provided by the platform. The use of this pattern provides several advantages to the system, such as: It increases the security of the system by reducing the gateways to the outside, since the only way to interact with the microservices is through the Api Gateway.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_03, C_04</t>
+          <t>C_05, Security</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_06, P_03</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M01_C09, *CF_M01_C10</t>
+          <t>*CF_M01_C07</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AD06</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8882</v>
+        <v>0.9235</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>NestJS framework has been used to develop the different services. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD04</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9373</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>És solament l’Api Gateway que s’encarrega de l’autorització i el SSL amb el client.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>AU_06</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>*CF_M01_C07</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>CF_M01_AU10</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>43</v>
-      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8603</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>AWS is the set of cloud computing services that allows the creation of scalable and highly available applications. It has been decided to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C_03, C_04</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>*CF_M01_C09, *CF_M01_C10</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD05</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9589</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>TypeScript has been chosen, and not JavaScript, because it is the default language for NestJS and because thanks to its static typing it allows the detection of errors at compile time.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU34</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>To make the data transmission as fast as possible, two Amazon services have been used, which allow us to perform a transmission in near real-time.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C_01, Performance</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>AU_20, AU_21</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1152,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,52 +1455,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform. [...] Augmenta la seguretat del sistema al reduir les portes d’enllaç amb l’exterior, ja que l’única manera d’interactuar amb els microserveis és a través de l’Api Gateway.</t>
+          <t>The platform is a web service that follows the client-server architecture, and for the client-server model, a 3-layer architecture is used, where the system is divided into 3 layers: the presentation layer, the business layer, and the data layer.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_05, Security</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_03, AU_06</t>
+          <t>P_01, P_02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AD06</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8214</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L’objectiu d’aquests serveis és formar un data lake on s’emmagatzemi tots els històrics per poder processar-los en el mòdul analític.</t>
+          <t>The objective of these services is to form a data lake where all history is stored to be able to process them in the analytical module.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R_24, R_25, C_03, C_04</t>
+          <t>C_03, C_04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_12, AU_16, AU_18, AU_19</t>
+          <t>AU_12, AU_16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1259,77 +1514,42 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5952</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Perquè sigui la transmissió de dades la més ràpida possible s’han fet ús de dos serveis d’Amazon, que ens permeten realitzar una transmissió en quasi temps real.</t>
+          <t>Amazon Athena is a serverless service, which means it is not necessary to manage the infrastructure when there is an increase in the set of data and users. In addition, to obtain data quickly, Athena performs queries in parallel.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_01</t>
+          <t>C_01, Performance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AU_20, AU_21</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5958</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>S’ha decidit la utilització d’aquest llenguatge [TypeScript], i no JavaScript, ja que és el llenguatge per defecte per NestJS i perquè gràcies al seu tipatge estàtic permet la detecció d’errors en temps de compilació.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_01</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AU_13, AU_14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5849</v>
+        <v>0.6741</v>
       </c>
     </row>
   </sheetData>
@@ -1409,11 +1629,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6217</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="3">
@@ -1442,11 +1662,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5718</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/decision/v1/CF_M01/run_1/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_1/CF_M01_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.625</v>
+        <v>0.3</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7143</v>
+        <v>0.4286</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9237</v>
+        <v>0.8681</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9651</v>
+        <v>0.9302</v>
       </c>
     </row>
     <row r="8">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.625</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7143</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,28 +755,28 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -792,31 +792,31 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7</v>
-      </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,36 +974,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8138</v>
+        <v>0.8486</v>
       </c>
       <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1012,19 +1012,21 @@
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>The only component that interacts directly with the presentation layer is the Api Gateway module. This is because the Api Gateway microservices design pattern is followed. This design pattern allows only one component to interact between users and the services provided by the platform. The use of this pattern provides several advantages to the system, such as: It increases the security of the system by reducing the gateways to the outside, since the only way to interact with the microservices is through the Api Gateway.</t>
+          <t>L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_05, Security</t>
+          <t>Security, Scalability, Availability and reliability</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1034,53 +1036,53 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M01_C07</t>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AD06</t>
+          <t>CF_M01_AD04</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9235</v>
+        <v>0.8673</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1100,21 +1102,21 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.8603</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>NestJS framework has been used to develop the different services. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Low price, Previous use by the company</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1124,17 +1126,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>*CF_M01_C11</t>
+          <t>*CF_M01_C09, *CF_M01_C10</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -1144,28 +1146,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9373</v>
+        <v>0.8882</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1179,222 +1181,52 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.8603</v>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>AWS is the set of cloud computing services that allows the creation of scalable and highly available applications. It has been decided to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+          <t>És solament l’Api Gateway que s’encarrega de l’autorització i el SSL amb el client.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>C_03, C_04</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_06, P_03</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>*CF_M01_C09, *CF_M01_C10</t>
+          <t>*CF_M01_C07</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CF_M01_AD05</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9589</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>TypeScript has been chosen, and not JavaScript, because it is the default language for NestJS and because thanks to its static typing it allows the detection of errors at compile time.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>*CF_M01_C11</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>CF_M01_AU34</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CF_M01_AD07</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9852</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>To make the data transmission as fast as possible, two Amazon services have been used, which allow us to perform a transmission in near real-time.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>C_01, Performance</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>AU_20, AU_21</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>CF_M01_C01</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1407,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1455,101 +1287,241 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The platform is a web service that follows the client-server architecture, and for the client-server model, a 3-layer architecture is used, where the system is divided into 3 layers: the presentation layer, the business layer, and the data layer.</t>
+          <t>Aquestes tecnologies són les mateixes de les quals s’utilitzen actualment a l’empresa de Waapiti.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>Waapiti</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01, P_02</t>
+          <t>AU_13, AU_14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AD06</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all history is stored to be able to process them in the analytical module.</t>
+          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_03, C_04</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_12, AU_16</t>
+          <t>P_02, AU_03, AU_04, AU_05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD06</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.635</v>
+        <v>0.6347</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amazon Athena is a serverless service, which means it is not necessary to manage the infrastructure when there is an increase in the set of data and users. In addition, to obtain data quickly, Athena performs queries in parallel.</t>
+          <t>Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_01, Performance</t>
+          <t>Microservices API Gateway design pattern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_06, P_03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6549</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Augmenta la seguretat del sistema al reduir les portes d’enllaç amb l’exterior, ja que l’única manera d’interactuar amb els microserveis és a través de l’Api Gateway.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_06, P_03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD02</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8393</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dona la capacitat de manegar caigudes parcials del sistema, manegant quins serveis estan en funcionament en tot moment.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Availability and reliability</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AU_06, P_03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD03</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7309</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aquesta base de dades està implementada en el servei RDS , que és un servei de base de dades relacional distribuït d’AWS.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RDS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>CF_M01_AD07</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0.6741</v>
+      <c r="G7" t="n">
+        <v>0.6366000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aquesta funció ens permet crear particions en S3, i d’aquesta manera crear subcarpetes, respecte a unes claus predefinides.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5784</v>
       </c>
     </row>
   </sheetData>
@@ -1563,7 +1535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1606,26 +1578,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+          <t>*CF_M01_C08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1633,40 +1605,104 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.635</v>
+        <v>0.7309</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_AD03</t>
+          <t>CF_M01_AD05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gives the ability to handle partial system crashes</t>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M01_C08</t>
+          <t>*CF_M01_C11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5718</v>
+        <v>0.5597</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6721</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6481</v>
       </c>
     </row>
   </sheetData>
